--- a/082626_005pc_ST_Cluster10_GUM.xlsx
+++ b/082626_005pc_ST_Cluster10_GUM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATDI\Rodney\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5858C3F-5AC9-4B4E-A555-5746A4D6D84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8045E052-269E-470E-A1D2-9B5E29EF4682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="210" windowWidth="18340" windowHeight="10240" xr2:uid="{44B78643-BDFE-409A-A60F-A57E530E0F62}"/>
+    <workbookView xWindow="20" yWindow="210" windowWidth="18340" windowHeight="10240" xr2:uid="{FBBC1B29-0BA7-45BF-A111-6625858D0C64}"/>
   </bookViews>
   <sheets>
     <sheet name="jtemp1000_130" sheetId="1" r:id="rId1"/>
@@ -1085,7 +1085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6C2490-18B1-4DFA-98E7-3A1DE04E0CF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E932F5-1389-4FA3-9341-EB7E4F099105}">
   <dimension ref="A1:AP33"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
@@ -1261,7 +1261,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O2">
-        <v>-178.38</v>
+        <v>-178.03</v>
       </c>
       <c r="P2" t="s">
         <v>45</v>
@@ -1321,7 +1321,7 @@
         <v>9294.06</v>
       </c>
       <c r="AI2">
-        <v>158.87</v>
+        <v>158.52000000000001</v>
       </c>
       <c r="AJ2">
         <v>112</v>
@@ -1389,7 +1389,7 @@
         <v>8192.6</v>
       </c>
       <c r="O3">
-        <v>-147.41</v>
+        <v>-147.29</v>
       </c>
       <c r="P3" t="s">
         <v>45</v>
@@ -1449,7 +1449,7 @@
         <v>8998.41</v>
       </c>
       <c r="AI3">
-        <v>128.94</v>
+        <v>128.82</v>
       </c>
       <c r="AJ3">
         <v>112</v>
@@ -1517,7 +1517,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O4">
-        <v>-182.94</v>
+        <v>-182.59</v>
       </c>
       <c r="P4" t="s">
         <v>45</v>
@@ -1577,7 +1577,7 @@
         <v>9294.06</v>
       </c>
       <c r="AI4">
-        <v>159.26</v>
+        <v>158.91</v>
       </c>
       <c r="AJ4">
         <v>112</v>
@@ -1645,7 +1645,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O5">
-        <v>-178.38</v>
+        <v>-178.03</v>
       </c>
       <c r="P5" t="s">
         <v>45</v>
@@ -1705,7 +1705,7 @@
         <v>9294.06</v>
       </c>
       <c r="AI5">
-        <v>158.87</v>
+        <v>158.52000000000001</v>
       </c>
       <c r="AJ5">
         <v>112</v>
@@ -1773,7 +1773,7 @@
         <v>8192.6</v>
       </c>
       <c r="O6">
-        <v>-147.41</v>
+        <v>-147.29</v>
       </c>
       <c r="P6" t="s">
         <v>45</v>
@@ -1833,7 +1833,7 @@
         <v>8998.41</v>
       </c>
       <c r="AI6">
-        <v>128.94</v>
+        <v>128.82</v>
       </c>
       <c r="AJ6">
         <v>112</v>
@@ -1901,7 +1901,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O7">
-        <v>-182.94</v>
+        <v>-182.59</v>
       </c>
       <c r="P7" t="s">
         <v>45</v>
@@ -1961,7 +1961,7 @@
         <v>9294.06</v>
       </c>
       <c r="AI7">
-        <v>159.26</v>
+        <v>158.91</v>
       </c>
       <c r="AJ7">
         <v>112</v>
@@ -2029,7 +2029,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O8">
-        <v>-184.24</v>
+        <v>-183.98</v>
       </c>
       <c r="P8" t="s">
         <v>45</v>
@@ -2089,7 +2089,7 @@
         <v>8865.48</v>
       </c>
       <c r="AI8">
-        <v>180.23</v>
+        <v>179.96</v>
       </c>
       <c r="AJ8">
         <v>112</v>
@@ -2157,7 +2157,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O9">
-        <v>-184.24</v>
+        <v>-183.98</v>
       </c>
       <c r="P9" t="s">
         <v>45</v>
@@ -2217,7 +2217,7 @@
         <v>8865.48</v>
       </c>
       <c r="AI9">
-        <v>180.23</v>
+        <v>179.96</v>
       </c>
       <c r="AJ9">
         <v>112</v>
@@ -2285,7 +2285,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O10">
-        <v>-123.3</v>
+        <v>-123.2</v>
       </c>
       <c r="P10" t="s">
         <v>45</v>
@@ -2345,7 +2345,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI10">
-        <v>130.32</v>
+        <v>130.22</v>
       </c>
       <c r="AJ10">
         <v>112</v>
@@ -2413,7 +2413,7 @@
         <v>8192.6</v>
       </c>
       <c r="O11">
-        <v>-122.94</v>
+        <v>-122.85</v>
       </c>
       <c r="P11" t="s">
         <v>45</v>
@@ -2473,7 +2473,7 @@
         <v>10668.44</v>
       </c>
       <c r="AI11">
-        <v>130.65</v>
+        <v>130.55000000000001</v>
       </c>
       <c r="AJ11">
         <v>112</v>
@@ -2541,7 +2541,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O12">
-        <v>-127.69</v>
+        <v>-127.59</v>
       </c>
       <c r="P12" t="s">
         <v>45</v>
@@ -2601,7 +2601,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI12">
-        <v>130.54</v>
+        <v>130.44</v>
       </c>
       <c r="AJ12">
         <v>112</v>
@@ -2669,7 +2669,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O13">
-        <v>-123.3</v>
+        <v>-123.2</v>
       </c>
       <c r="P13" t="s">
         <v>45</v>
@@ -2729,7 +2729,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI13">
-        <v>130.32</v>
+        <v>130.22</v>
       </c>
       <c r="AJ13">
         <v>112</v>
@@ -2797,7 +2797,7 @@
         <v>8192.6</v>
       </c>
       <c r="O14">
-        <v>-122.94</v>
+        <v>-122.85</v>
       </c>
       <c r="P14" t="s">
         <v>45</v>
@@ -2857,7 +2857,7 @@
         <v>10668.44</v>
       </c>
       <c r="AI14">
-        <v>130.65</v>
+        <v>130.55000000000001</v>
       </c>
       <c r="AJ14">
         <v>112</v>
@@ -2925,7 +2925,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O15">
-        <v>-127.69</v>
+        <v>-127.59</v>
       </c>
       <c r="P15" t="s">
         <v>45</v>
@@ -2985,7 +2985,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI15">
-        <v>130.54</v>
+        <v>130.44</v>
       </c>
       <c r="AJ15">
         <v>112</v>
@@ -3053,7 +3053,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O16">
-        <v>-137.65</v>
+        <v>-137.54</v>
       </c>
       <c r="P16" t="s">
         <v>45</v>
@@ -3113,7 +3113,7 @@
         <v>9137.35</v>
       </c>
       <c r="AI16">
-        <v>129.12</v>
+        <v>129.01</v>
       </c>
       <c r="AJ16">
         <v>112</v>
@@ -3181,7 +3181,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O17">
-        <v>-137.65</v>
+        <v>-137.54</v>
       </c>
       <c r="P17" t="s">
         <v>45</v>
@@ -3241,7 +3241,7 @@
         <v>9137.35</v>
       </c>
       <c r="AI17">
-        <v>129.12</v>
+        <v>129.01</v>
       </c>
       <c r="AJ17">
         <v>112</v>
@@ -3309,7 +3309,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O18">
-        <v>-199.25</v>
+        <v>-198.8</v>
       </c>
       <c r="P18" t="s">
         <v>45</v>
@@ -3369,7 +3369,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI18">
-        <v>179.54</v>
+        <v>179.08</v>
       </c>
       <c r="AJ18">
         <v>112</v>
@@ -3437,7 +3437,7 @@
         <v>8192.6</v>
       </c>
       <c r="O19">
-        <v>-198.54</v>
+        <v>-198.1</v>
       </c>
       <c r="P19" t="s">
         <v>45</v>
@@ -3497,7 +3497,7 @@
         <v>10668.44</v>
       </c>
       <c r="AI19">
-        <v>179.52</v>
+        <v>179.08</v>
       </c>
       <c r="AJ19">
         <v>112</v>
@@ -3565,7 +3565,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O20">
-        <v>-203.89</v>
+        <v>-203.43</v>
       </c>
       <c r="P20" t="s">
         <v>45</v>
@@ -3625,7 +3625,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI20">
-        <v>180.01</v>
+        <v>179.55</v>
       </c>
       <c r="AJ20">
         <v>112</v>
@@ -3693,7 +3693,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O21">
-        <v>-199.25</v>
+        <v>-198.8</v>
       </c>
       <c r="P21" t="s">
         <v>45</v>
@@ -3753,7 +3753,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI21">
-        <v>179.54</v>
+        <v>179.08</v>
       </c>
       <c r="AJ21">
         <v>112</v>
@@ -3821,7 +3821,7 @@
         <v>8192.6</v>
       </c>
       <c r="O22">
-        <v>-198.54</v>
+        <v>-198.1</v>
       </c>
       <c r="P22" t="s">
         <v>45</v>
@@ -3881,7 +3881,7 @@
         <v>10668.44</v>
       </c>
       <c r="AI22">
-        <v>179.52</v>
+        <v>179.08</v>
       </c>
       <c r="AJ22">
         <v>112</v>
@@ -3949,7 +3949,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O23">
-        <v>-203.89</v>
+        <v>-203.43</v>
       </c>
       <c r="P23" t="s">
         <v>45</v>
@@ -4009,7 +4009,7 @@
         <v>10432.81</v>
       </c>
       <c r="AI23">
-        <v>180.01</v>
+        <v>179.55</v>
       </c>
       <c r="AJ23">
         <v>112</v>
@@ -4077,7 +4077,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O24">
-        <v>-142.11000000000001</v>
+        <v>-141.96</v>
       </c>
       <c r="P24" t="s">
         <v>45</v>
@@ -4137,7 +4137,7 @@
         <v>22009.54</v>
       </c>
       <c r="AI24">
-        <v>136.33000000000001</v>
+        <v>136.19</v>
       </c>
       <c r="AJ24">
         <v>112</v>
@@ -4205,7 +4205,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O25">
-        <v>-142.11000000000001</v>
+        <v>-141.96</v>
       </c>
       <c r="P25" t="s">
         <v>45</v>
@@ -4265,7 +4265,7 @@
         <v>22009.54</v>
       </c>
       <c r="AI25">
-        <v>136.33000000000001</v>
+        <v>136.19</v>
       </c>
       <c r="AJ25">
         <v>112</v>
@@ -4333,16 +4333,16 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O26">
-        <v>-85.94</v>
+        <v>-85.81</v>
       </c>
       <c r="P26" t="s">
         <v>45</v>
       </c>
       <c r="Q26">
-        <v>7.02</v>
+        <v>7.13</v>
       </c>
       <c r="R26">
-        <v>7.02</v>
+        <v>7.13</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>18299.93</v>
       </c>
       <c r="AI26">
-        <v>134.83000000000001</v>
+        <v>134.69</v>
       </c>
       <c r="AJ26">
         <v>112</v>
@@ -4461,16 +4461,16 @@
         <v>8192.6</v>
       </c>
       <c r="O27">
-        <v>-85.71</v>
+        <v>-85.58</v>
       </c>
       <c r="P27" t="s">
         <v>45</v>
       </c>
       <c r="Q27">
-        <v>7.21</v>
+        <v>7.31</v>
       </c>
       <c r="R27">
-        <v>9.68</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>18621.02</v>
       </c>
       <c r="AI27">
-        <v>135.11000000000001</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="AJ27">
         <v>112</v>
@@ -4589,16 +4589,16 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O28">
-        <v>-90.33</v>
+        <v>-90.19</v>
       </c>
       <c r="P28" t="s">
         <v>45</v>
       </c>
       <c r="Q28">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="R28">
-        <v>10.32</v>
+        <v>10.44</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>18299.93</v>
       </c>
       <c r="AI28">
-        <v>135.04</v>
+        <v>134.91</v>
       </c>
       <c r="AJ28">
         <v>112</v>
@@ -4845,7 +4845,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O30">
-        <v>-125.97</v>
+        <v>-125.83</v>
       </c>
       <c r="P30" t="s">
         <v>45</v>
@@ -4905,7 +4905,7 @@
         <v>22023.41</v>
       </c>
       <c r="AI30">
-        <v>136.58000000000001</v>
+        <v>136.44</v>
       </c>
       <c r="AJ30">
         <v>112</v>
@@ -4973,7 +4973,7 @@
         <v>8064.1840000000002</v>
       </c>
       <c r="O31">
-        <v>-148.76</v>
+        <v>-148.4</v>
       </c>
       <c r="P31" t="s">
         <v>45</v>
@@ -5033,7 +5033,7 @@
         <v>11106.01</v>
       </c>
       <c r="AI31">
-        <v>154.84</v>
+        <v>154.47999999999999</v>
       </c>
       <c r="AJ31">
         <v>112</v>
@@ -5101,7 +5101,7 @@
         <v>8192.6</v>
       </c>
       <c r="O32">
-        <v>-123.88</v>
+        <v>-123.73</v>
       </c>
       <c r="P32" t="s">
         <v>45</v>
@@ -5161,7 +5161,7 @@
         <v>11398.54</v>
       </c>
       <c r="AI32">
-        <v>130.66</v>
+        <v>130.51</v>
       </c>
       <c r="AJ32">
         <v>112</v>
@@ -5229,7 +5229,7 @@
         <v>8267.7000000000007</v>
       </c>
       <c r="O33">
-        <v>-153.28</v>
+        <v>-152.91999999999999</v>
       </c>
       <c r="P33" t="s">
         <v>45</v>
@@ -5289,7 +5289,7 @@
         <v>11106.01</v>
       </c>
       <c r="AI33">
-        <v>155.19999999999999</v>
+        <v>154.84</v>
       </c>
       <c r="AJ33">
         <v>112</v>
@@ -5314,7 +5314,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{6D6C2490-18B1-4DFA-98E7-3A1DE04E0CF6}"/>
+  <autoFilter ref="A1:AP1" xr:uid="{48E932F5-1389-4FA3-9341-EB7E4F099105}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>